--- a/runs/AP-run-2026-09-21-oneal.xlsx
+++ b/runs/AP-run-2026-09-21-oneal.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Exception counts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AP run'!$A$1:$Q$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AP run'!$A$1:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -944,8 +944,521 @@
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>O'Neal Steel - Dallas (GP)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>15460544</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58920</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Finished bill (Invoice_Type 3). Header PO set=58920. Select Receipts 23730 240@0.2688 on PO 58920. Invoice #=15460544 (exact PDF). Fees=none (Additional Charge Fees id 11, not missing merch lines / not PPV). PPV=none. Attach status=attached. Finish Select Receipts selected ids=[23730] fees=none ppv=none. Flag status=entered-in-ai.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
+        <v>10174</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>API Agent - 9/21/26 O'Neal (722)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>attached</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>entered-with-issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>O'Neal Steel - Dallas (GP)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>15460995</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59085</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6954.21</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>category=missing_receipt; owner=Anthony. HOLD (receipt): no open receipt leftover on PO 59085 for O'Neal invoice #15460995. Do not first-open guess. Anthony: receiving must receive the PO so AP can Select Receipts. Comments_1 names Anthony (mention-id unproven). Do not Transfer AP. Outlook AI HOLD. Flag status=entered-with-issues. Comments_1 missing_receipt status=added tab=Comments tab persisted Anthony (list Comments_1 item 929, plain text (no mention-node)). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored. transfer_ap=False mention_id=None owner=Anthony mail_send=False.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>missing_receipt</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>10175</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>API Agent - 9/21/26 O'Neal (722)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>attached</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>entered-with-issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>O'Neal Steel - Dallas (GP)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>15461007</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>59086</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Finished bill (Invoice_Type 3). Header PO set=59086. Select Receipts already-selected on PO 59086. Invoice #=15461007 (exact PDF). Amount=67.38 after rounding PPV +0.18. Fees=none. Attach status=attached. Flag status=entered-with-issues (parent siblings not all Success).</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
+        <v>10176</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>API Agent - 9/21/26 O'Neal (722)</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>attached</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>entered-with-issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>O'Neal Steel - Dallas (GP)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>15461157</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59092</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1978.91</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Finished bill (Invoice_Type 3). Header PO set=59092. Select Receipts 23799 4@494.7275 on PO 59092. Invoice #=15461157 (exact PDF). Fees=none (Additional Charge Fees id 11, not missing merch lines / not PPV). PPV=none. Attach status=attached. Flag status=entered-in-ai.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
+        <v>10177</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>API Agent - 9/21/26 O'Neal (722)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>attached</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>entered-with-issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>O'Neal Steel - Dallas (GP)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>15476365</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>59070</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1115.68</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>category=missing_receipt; owner=Anthony. HOLD (receipt): no open receipt leftover on PO 59070 for O'Neal invoice #15476365. Do not first-open guess. Anthony: receiving must receive the PO so AP can Select Receipts. Comments_1 names Anthony (mention-id unproven). Do not Transfer AP. Outlook AI HOLD. Flag status=entered-with-issues. Comments_1 missing_receipt status=added tab=Comments tab persisted Anthony (list Comments_1 item 930, plain text (no mention-node)). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored. transfer_ap=False mention_id=None owner=Anthony mail_send=False.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>missing_receipt</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>10178</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>API Agent - 9/21/26 O'Neal (722)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>attached</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>entered-with-issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>O'Neal Steel - Dallas (GP)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>15476879</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59236</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>245.28</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Finished bill (Invoice_Type 3). Header PO set=59236. Select Receipts 24374 on PO 59236. Invoice #=15476879 (exact PDF). Amount=245.28 after rounding PPV -0.04 (in-gate, not $75). Returned from Transfer AP 375 to 722. Attach status=attached. Parent Outlook Entered with issues (15476365 still HOLD).</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
+        <v>10179</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>API Agent - 9/21/26 O'Neal (722)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>attached</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>entered-with-issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>O'Neal Steel - Dallas (GP)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>15477248</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59246</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>152.88</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Finished bill (Invoice_Type 3). Header PO set=59246. Select Receipts 24364 on PO 59246. Invoice #=15477248 (exact PDF). Amount=152.88 after rounding PPV +1.20 (in-gate, not $75). Returned from Transfer AP 375 to 722. Attach status=attached. Parent Outlook Entered with issues (15476365 still HOLD).</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
+        <v>10180</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>API Agent - 9/21/26 O'Neal (722)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>attached</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>entered-with-issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q6"/>
+  <autoFilter ref="A1:Q13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -982,7 +1495,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">

--- a/runs/AP-run-2026-09-21-oneal.xlsx
+++ b/runs/AP-run-2026-09-21-oneal.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Exception counts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AP run'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AP run'!$A$1:$Q$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -588,17 +588,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>category=missing_receipt; owner=Ruben Perez. HOLD (receipt): no open receipt leftover on PO 59156 for O'Neal invoice #15469453. Do not first-open guess. Ruben Perez: receiving must receive the PO so AP can Select Receipts. Comments_1 names Ruben Perez (mention-id unproven). Do not Transfer AP. Outlook AI HOLD. Flag status=entered-with-issues. Comments_1 missing_receipt status=added tab=Comments tab persisted Ruben Perez (list Comments_1 item 894, plain text (no mention-node)). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored. transfer_ap=False mention_id=None plain=True mail_send=False.</t>
+          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59156 has open leftovers (24025-24029, 24052, 24053) but they do not match PDF plate lines (no Select). Comments_1 Anthony plain added (mention-id unknown). Stay 722. Do not invent Success.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>missing_receipt</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Ruben Perez</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
@@ -647,11 +647,7 @@
           <t>15457895</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>59068</t>
@@ -660,32 +656,24 @@
       <c r="E3" s="2" t="n">
         <v>687.26</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Success</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>category=price_variance; owner=Shawn McKibben. HOLD (price-does-not-match): leftover vs invoice line is over the PPV gate. Do not Select Receipts on that line. @Shawn McKibben: purchasing must unreceive, change the PO price, and re-receive. Outlook AI HOLD. Flag status=entered-with-issues. Transfer AP status=moved batch_id=375 comment='Comments tab persisted @Shawn McKibben (list Comments_1 item 895, mention-node id 104). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored.' @mention=Comments tab persisted @Shawn McKibben (list Comments_1 item 895, mention-node id 104). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored..</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>price_variance</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Shawn McKibben</t>
-        </is>
-      </c>
+          <t>Finished bill. Rounding/in-gate PPV -0.10 under $75. Amount=687.26. Moved to 722={'status': 'moved', 'put': 200, 'error': ''}.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="n">
         <v>10161</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>TRANSFER AP (375)</t>
+          <t>API Agent - 9/21/26 O'Neal (722)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -695,7 +683,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -746,17 +734,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>category=price_variance; owner=Shawn McKibben. HOLD (price-does-not-match): leftover vs invoice line is over the PPV gate. Do not Select Receipts on that line. @Shawn McKibben: purchasing must unreceive, change the PO price, and re-receive. Outlook AI HOLD. Flag status=entered-with-issues. Transfer AP status=moved batch_id=375 comment='Comments tab persisted @Shawn McKibben (list Comments_1 item 896, mention-node id 104). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored.' @mention=Comments tab persisted @Shawn McKibben (list Comments_1 item 896, mention-node id 104). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored..</t>
+          <t>category=missing_po; owner=Misty McCoy / Transfer AP. HOLD price_variance. PO 59070 leftovers 23581-23584 still over the $75 PPV gate (select-zero). Receipts not selected. Left on Transfer AP 375 for Treyce/Shawn. Do not invent Success.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>price_variance</t>
+          <t>missing_po</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Shawn McKibben</t>
+          <t>Misty McCoy / Transfer AP</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -825,17 +813,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>category=missing_receipt; owner=Ruben Perez. HOLD (receipt): no open receipt leftover on PO 58912 for O'Neal invoice #15464707. Do not first-open guess. Ruben Perez: receiving must receive the PO so AP can Select Receipts. Comments_1 names Ruben Perez (mention-id unproven). Do not Transfer AP. Outlook AI HOLD. Flag status=entered-with-issues. Comments_1 missing_receipt status=added tab=Comments tab persisted Ruben Perez (list Comments_1 item 897, plain text (no mention-node)). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored. transfer_ap=False mention_id=None plain=True mail_send=False.</t>
+          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 58912 has open leftovers (23096, 23874, 23875, 23923, 23983, 23985) but they do not match PDF lines (no Select). Comments_1 Anthony plain added. Stay 722.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>missing_receipt</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Ruben Perez</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -1046,17 +1034,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>category=missing_receipt; owner=Anthony. HOLD (receipt): no open receipt leftover on PO 59085 for O'Neal invoice #15460995. Do not first-open guess. Anthony: receiving must receive the PO so AP can Select Receipts. Comments_1 names Anthony (mention-id unproven). Do not Transfer AP. Outlook AI HOLD. Flag status=entered-with-issues. Comments_1 missing_receipt status=added tab=Comments tab persisted Anthony (list Comments_1 item 929, plain text (no mention-node)). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored. transfer_ap=False mention_id=None owner=Anthony mail_send=False.</t>
+          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59085 leftovers include 23932 (already on 10164) plus 23933/23934; none newly selectable for 15460995. Comments_1 Anthony already-on-tab. Stay 722.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>missing_receipt</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -1267,17 +1255,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>category=missing_receipt; owner=Anthony. HOLD (receipt): no open receipt leftover on PO 59070 for O'Neal invoice #15476365. Do not first-open guess. Anthony: receiving must receive the PO so AP can Select Receipts. Comments_1 names Anthony (mention-id unproven). Do not Transfer AP. Outlook AI HOLD. Flag status=entered-with-issues. Comments_1 missing_receipt status=added tab=Comments tab persisted Anthony (list Comments_1 item 930, plain text (no mention-node)). User-alert/notify API not confirmed — dedicated GET comments/mentions/notifications are 404. Header Comments string is the wrong surface and is ignored. transfer_ap=False mention_id=None owner=Anthony mail_send=False.</t>
+          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59070 leftovers 23581-23584 are the same over-gate pool as 10162; no match for $1115.68. Comments_1 Anthony already-on-tab. Stay 722. Sibling 15457895 is now Success; parent Outlook stays Entered with issues.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>missing_receipt</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
@@ -1457,8 +1445,67 @@
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>O'Neal Steel - Dallas (GP)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>15447737</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58979</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1683.01</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Already-Success O'Neal on Transfer AP 375 (older header 10079). Amount=1683.01 matches verification. 4 receipts selected + 1 charge. Moved to API Agent - 9/21/26 O'Neal (722). Not a new enter. Packing slip not attached (receiving@ not reachable on this AP Graph client).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
+        <v>10079</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>API Agent - 9/21/26 O'Neal (722)</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1 charge already posted</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>attached</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q13"/>
+  <autoFilter ref="A1:Q14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1491,7 +1538,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>missing_receipt</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1501,11 +1548,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>price_variance</t>
+          <t>missing_po</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/runs/AP-run-2026-09-21-oneal.xlsx
+++ b/runs/AP-run-2026-09-21-oneal.xlsx
@@ -634,7 +634,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOZ_uDcAAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -701,7 +705,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOQsGW4AAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -780,7 +788,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=move-skipped-already mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOQsGW4AAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -859,7 +871,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOVX234AAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -930,7 +946,11 @@
           <t>entered-in-ai</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=move-skipped-already mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOVX234AAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1001,7 +1021,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOQsGYLAAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1080,7 +1104,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=move-skipped-already mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOQsGYLAAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1151,7 +1179,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=move-skipped-already mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOQsGYLAAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1222,7 +1254,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=move-skipped-already mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOQsGYLAAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1301,7 +1337,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOeCmQ1AAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1372,7 +1412,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=move-skipped-already mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOeCmQ1AAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1443,7 +1487,11 @@
           <t>entered-with-issues</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=move-skipped-already mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOeCmQ1AAA=.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1502,7 +1550,11 @@
       </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOMxVrbAAA=.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q14"/>

--- a/runs/AP-run-2026-09-21-oneal.xlsx
+++ b/runs/AP-run-2026-09-21-oneal.xlsx
@@ -588,17 +588,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59156 has open leftovers (24025-24029, 24052, 24053) but they do not match PDF plate lines (no Select). Comments_1 Anthony plain added (mention-id unknown). Stay 722. Do not invent Success.</t>
+          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59156 has open leftovers (24025-24029, 24052, 24053) but they do not match PDF plate lines (no Select). Comments_1 Anthony plain added (mention-id unknown). Stay 722. Do not invent Success. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>missing_receipt</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>API Agent - 9/21/26 O'Neal (722)</t>
+          <t>Transfer AP (375)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOZ_uDcAAA=.</t>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOZ_uDcAAA=. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 58912 has open leftovers (23096, 23874, 23875, 23923, 23983, 23985) but they do not match PDF lines (no Select). Comments_1 Anthony plain added. Stay 722.</t>
+          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 58912 has open leftovers (23096, 23874, 23875, 23923, 23983, 23985) but they do not match PDF lines (no Select). Comments_1 Anthony plain added. Stay 722. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>missing_receipt</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>API Agent - 9/21/26 O'Neal (722)</t>
+          <t>Transfer AP (375)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOVX234AAA=.</t>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOVX234AAA=. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59085 leftovers include 23932 (already on 10164) plus 23933/23934; none newly selectable for 15460995. Comments_1 Anthony already-on-tab. Stay 722.</t>
+          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59085 leftovers include 23932 (already on 10164) plus 23933/23934; none newly selectable for 15460995. Comments_1 Anthony already-on-tab. Stay 722. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>missing_receipt</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>API Agent - 9/21/26 O'Neal (722)</t>
+          <t>Transfer AP (375)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=move-skipped-already mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOQsGYLAAA=.</t>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=move-skipped-already mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOQsGYLAAA=. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
     </row>
@@ -1291,17 +1291,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59070 leftovers 23581-23584 are the same over-gate pool as 10162; no match for $1115.68. Comments_1 Anthony already-on-tab. Stay 722. Sibling 15457895 is now Success; parent Outlook stays Entered with issues.</t>
+          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59070 leftovers 23581-23584 are the same over-gate pool as 10162; no match for $1115.68. Comments_1 Anthony already-on-tab. Stay 722. Sibling 15457895 is now Success; parent Outlook stays Entered with issues. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>missing_receipt</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>API Agent - 9/21/26 O'Neal (722)</t>
+          <t>Transfer AP (375)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOeCmQ1AAA=.</t>
+          <t>NOTE-52 Fort Worth 9 - FORT WORTH ARCHIVE move=moved-fort-worth mid=AAMkAGQyODM5ZWI1LTQ0NDAtNDZiOS1hYTIzLTdjOGM3NDRlNjQ4MgBGAAAAAAAggjN_BHG4TI2Iz-JKRqfaBwDXcyWbp23lSoY0i7GBv6N_AAAAAAEMAADXcyWbp23lSoY0i7GBv6N_AAOeCmQ1AAA=. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
     </row>

--- a/runs/AP-run-2026-09-21-oneal.xlsx
+++ b/runs/AP-run-2026-09-21-oneal.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="AP run" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Exception counts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AP run'!$A$1:$Q$14</definedName>
@@ -68,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -82,7 +81,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,10 +465,10 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Vendor</t>
@@ -588,7 +586,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59156 has open leftovers (24025-24029, 24052, 24053) but they do not match PDF plate lines (no Select). Comments_1 Anthony plain added (mention-id unknown). Stay 722. Do not invent Success. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
+          <t>HOLD missing_receipt after leftover recheck. PO 59156 has open leftovers (24025-24029, 24052, 24053) but they do not match PDF plate lines (no Select). Comments_1 Anthony plain added (mention-id unknown). Stay 722. Do not invent Success. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -606,7 +604,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Transfer AP (375)</t>
+          <t>TRANSFER AP (375)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -742,17 +740,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>category=missing_po; owner=Misty McCoy / Transfer AP. HOLD price_variance. PO 59070 leftovers 23581-23584 still over the $75 PPV gate (select-zero). Receipts not selected. Left on Transfer AP 375 for Treyce/Shawn. Do not invent Success.</t>
+          <t>HOLD price_variance. PO 59070 leftovers 23581-23584 still over the $75 PPV gate (select-zero). Receipts not selected. Left on Transfer AP 375 for Treyce/Shawn. Do not invent Success.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>missing_po</t>
+          <t>price_variance</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Misty McCoy / Transfer AP</t>
+          <t>Shawn McKibben</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -825,7 +823,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 58912 has open leftovers (23096, 23874, 23875, 23923, 23983, 23985) but they do not match PDF lines (no Select). Comments_1 Anthony plain added. Stay 722. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
+          <t>HOLD missing_receipt after leftover recheck. PO 58912 has open leftovers (23096, 23874, 23875, 23923, 23983, 23985) but they do not match PDF lines (no Select). Comments_1 Anthony plain added. Stay 722. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -843,7 +841,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Transfer AP (375)</t>
+          <t>TRANSFER AP (375)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -1058,7 +1056,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59085 leftovers include 23932 (already on 10164) plus 23933/23934; none newly selectable for 15460995. Comments_1 Anthony already-on-tab. Stay 722. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
+          <t>HOLD missing_receipt after leftover recheck. PO 59085 leftovers include 23932 (already on 10164) plus 23933/23934; none newly selectable for 15460995. Comments_1 Anthony already-on-tab. Stay 722. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1076,7 +1074,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Transfer AP (375)</t>
+          <t>TRANSFER AP (375)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1291,7 +1289,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>category=other; owner=AP. HOLD missing_receipt after leftover recheck. PO 59070 leftovers 23581-23584 are the same over-gate pool as 10162; no match for $1115.68. Comments_1 Anthony already-on-tab. Stay 722. Sibling 15457895 is now Success; parent Outlook stays Entered with issues. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
+          <t>HOLD missing_receipt after leftover recheck. PO 59070 leftovers 23581-23584 are the same over-gate pool as 10162; no match for $1115.68. Comments_1 Anthony already-on-tab. Stay 722. Sibling 15457895 is now Success; parent Outlook stays Entered with issues. Kyle 2026-09-22 NOTE-53 missing_receipt → Transfer AP 722→375 status=moved.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1309,7 +1307,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Transfer AP (375)</t>
+          <t>TRANSFER AP (375)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1560,54 +1558,4 @@
   <autoFilter ref="A1:Q14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Exception category</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>missing_po</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>